--- a/data/trans_camb/P1801_2016_2023-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1801_2016_2023-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-5,13</t>
+          <t>-7,68</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,32</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,66</t>
+          <t>-4,46</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 4,14</t>
+          <t>-14,12; 0,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 9,01</t>
+          <t>-9,24; 8,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 2,78</t>
+          <t>-10,25; 1,59</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-19,38%</t>
+          <t>-29,05%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-0,63%</t>
+          <t>-0,78%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-10,94%</t>
+          <t>-13,32%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,02; 18,12</t>
+          <t>-51,03; 2,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 23,77</t>
+          <t>-20,84; 21,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 8,53</t>
+          <t>-29,25; 5,42</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-11,98</t>
+          <t>-7,58</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>-1,64</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 11,63</t>
+          <t>-3,33; 11,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,95; -3,5</t>
+          <t>-13,5; -1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 1,85</t>
+          <t>-6,88; 2,77</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-24,3%</t>
+          <t>-15,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-8,79%</t>
+          <t>-4,14%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 42,28</t>
+          <t>-10,46; 39,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,84; -7,31</t>
+          <t>-26,37; -3,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 4,52</t>
+          <t>-16,81; 7,3</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-4,13</t>
+          <t>-4,2</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-2,44</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 7,15</t>
+          <t>-6,48; 4,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 1,23</t>
+          <t>-9,24; 0,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,85</t>
+          <t>-6,35; 1,28</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>-1,78%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-7,93%</t>
+          <t>-8,08%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-2,44%</t>
+          <t>-5,2%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 18,52</t>
+          <t>-14,15; 11,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 2,45</t>
+          <t>-16,86; 1,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 6,44</t>
+          <t>-12,75; 2,82</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>18,34</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>4,74</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>4,35</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 40,25</t>
+          <t>-1,54; 9,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 8,67</t>
+          <t>-0,34; 9,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 26,81</t>
+          <t>0,65; 7,87</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,5; 88,99</t>
+          <t>-3,07; 21,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 17,58</t>
+          <t>-0,65; 19,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 57,36</t>
+          <t>1,07; 16,3</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-1,92</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-1,65</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 5,92</t>
+          <t>-7,79; 5,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 2,76</t>
+          <t>-7,07; 3,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 3,04</t>
+          <t>-5,87; 2,08</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-0,15%</t>
+          <t>-2,1%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-3,63%</t>
+          <t>-2,9%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-2,19%</t>
+          <t>-2,66%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 10,91</t>
+          <t>-12,7; 9,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 4,55</t>
+          <t>-10,14; 4,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 5,12</t>
+          <t>-8,95; 3,57</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>-8,88</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>-6,28</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 3,38</t>
+          <t>-9,53; 3,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 17,85</t>
+          <t>-13,88; -3,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 17,54</t>
+          <t>-10,21; -1,56</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-4,19%</t>
+          <t>-4,86%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>-11,72%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>-8,73%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 5,33</t>
+          <t>-13,27; 5,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 26,1</t>
+          <t>-17,65; -4,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 25,81</t>
+          <t>-13,84; -2,26</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-2,37</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-1,31</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 5,32</t>
+          <t>-9,12; 4,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 4,98</t>
+          <t>-6,0; 5,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 2,91</t>
+          <t>-6,08; 3,24</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-2,27%</t>
+          <t>-3,15%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-1,33%</t>
+          <t>-0,91%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-1,68%</t>
+          <t>-1,79%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 7,37</t>
+          <t>-11,55; 6,1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 7,47</t>
+          <t>-7,85; 8,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 4,14</t>
+          <t>-7,96; 4,67</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,83; 17,56</t>
+          <t>-1,28; 4,09</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 8,18</t>
+          <t>-3,51; 1,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 9,28</t>
+          <t>-1,6; 1,76</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-0,02%</t>
+          <t>-2,11%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>3,85; 36,71</t>
+          <t>-2,61; 9,01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 14,48</t>
+          <t>-5,98; 2,03</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 18,12</t>
+          <t>-3,04; 3,45</t>
         </is>
       </c>
     </row>
